--- a/agent_runs/manjidiwang/episodes/ep07/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep07/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>会议任命之争（，总时长：11秒，镜头数：5个）</t>
+          <t>会议任命之争</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>朱天和发难（，总时长：14秒，镜头数：5个）</t>
+          <t>朱天和发难</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>三方对峙（，总时长：12秒，镜头数：4个）</t>
+          <t>三方对峙</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>茶桌试探（，总时长：13秒，镜头数：6个）</t>
+          <t>茶桌试探</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>文件揭秘（，总时长：11秒，镜头数：4个）</t>
+          <t>文件揭秘</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>利用坦白（，总时长：11秒，镜头数：5个）</t>
+          <t>利用坦白</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -372,7 +372,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>威胁升级（，总时长：14秒，镜头数：4个）</t>
+          <t>威胁升级</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -420,7 +420,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>成交定局（，总时长：14秒，镜头数：5个）</t>
+          <t>成交定局</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>田立民暗算（，总时长：11秒，镜头数：4个）</t>
+          <t>田立民暗算</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -516,7 +516,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>内卫到手（，总时长：10秒，镜头数：4个）</t>
+          <t>内卫到手</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>修罗场入局（，总时长：12秒，镜头数：5个）</t>
+          <t>修罗场入局</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
